--- a/artfynd/A 9453-2020 artfynd.xlsx
+++ b/artfynd/A 9453-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9453-2020 artfynd.xlsx
+++ b/artfynd/A 9453-2020 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>78458633</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317677.5307515369</v>
+        <v>317678</v>
       </c>
       <c r="R4" t="n">
-        <v>6591628.422686031</v>
+        <v>6591628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,19 +1017,9 @@
           <t>2019-06-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
